--- a/data/trans_camb/IP1014-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,0</t>
+          <t>-2,94; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,62</t>
+          <t>-0,92; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 6,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,02</t>
+          <t>-1,72; 3,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-4,27; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,09</t>
+          <t>-0,57; 3,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 0,0</t>
+          <t>-7,84; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 6,46</t>
+          <t>-3,43; 5,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,0</t>
+          <t>-5,62; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,5</t>
+          <t>-1,78; 2,9</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,18</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 6,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,86</t>
+          <t>-1,57; 0,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,0</t>
+          <t>-2,49; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,44</t>
+          <t>-0,77; 0,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,0</t>
+          <t>-1,29; 0,0</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>-2,06; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,14</t>
+          <t>-1,7; 0,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,4</t>
+          <t>-1,05; 0,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,0</t>
+          <t>-1,45; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,27 +1879,27 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,53</t>
+          <t>-0,19; 0,51</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,55; 0,0</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,74</t>
+          <t>-0,48; 0,74</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,28</t>
+          <t>-0,77; 0,24</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,46</t>
+          <t>-0,21; 0,48</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 393,76</t>
+          <t>-65,31; 392,31</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 223,56</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-55,95; 341,17</t>
+          <t>-59,76; 329,97</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 105,91</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Provincia-trans_camb.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,19</t>
+          <t>-1,78; 1,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,0</t>
+          <t>-2,96; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,63</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,05</t>
+          <t>-1,74; 2,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,0</t>
+          <t>-4,23; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,05</t>
+          <t>-0,43; 3,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-2,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 0,0</t>
+          <t>-6,36; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 5,65</t>
+          <t>-3,49; 5,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,0</t>
+          <t>-4,03; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,9</t>
+          <t>-1,76; 2,93</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>0,0; 7,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>0,0; 5,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
     </row>
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,87</t>
+          <t>-1,58; 0,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,0</t>
+          <t>-3,14; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,44</t>
+          <t>-1,03; 0,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,0</t>
+          <t>-1,47; 0,0</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,0</t>
+          <t>-1,87; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,0</t>
+          <t>-2,23; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,79</t>
+          <t>-1,31; 0,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,4</t>
+          <t>-1,04; 0,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,0</t>
+          <t>-1,24; 0,0</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,51</t>
+          <t>-0,19; 0,57</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,0</t>
+          <t>-0,5; 0,0</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,74</t>
+          <t>-0,44; 0,79</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,24</t>
+          <t>-0,86; 0,24</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,48</t>
+          <t>-0,2; 0,54</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,09</t>
+          <t>-0,45; 0,12</t>
         </is>
       </c>
     </row>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 392,31</t>
+          <t>-67,96; 474,2</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 223,56</t>
+          <t>-100,0; 206,35</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 329,97</t>
+          <t>-55,86; 368,82</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 234,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1014-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1014-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,79; 1,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,98; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,61</t>
+          <t>-0,92; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-0,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,38%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,72</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,9</t>
+          <t>-1,72; 3,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,95</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,51</t>
+          <t>-0,59; 3,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,57</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,9; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,27; 6,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 5,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,0</t>
+          <t>-4,37; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,93</t>
+          <t>-1,85; 3,5</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>75,7%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>75,7%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2,28</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2,28</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,22 +1567,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,0; 0,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-14,5%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-14,5%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,03</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,41</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-0,41</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,0</t>
+          <t>-1,31; 1,14</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,0</t>
+          <t>-2,15; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,79</t>
+          <t>-2,28; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-1,91; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,4</t>
+          <t>-1,03; 0,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,0</t>
+          <t>-1,46; 0,0</t>
         </is>
       </c>
     </row>
@@ -1761,17 +1761,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-7,97%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-7,97%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,57</t>
+          <t>-0,47; 0,74</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,0</t>
+          <t>-0,75; 0,28</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,79</t>
+          <t>-0,16; 0,53</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,24</t>
+          <t>-0,47; 0,0</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,54</t>
+          <t>-0,26; 0,46</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,12</t>
+          <t>-0,48; 0,09</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>33,32%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-43,06%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>100,93%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>33,32%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-43,06%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-64,48; 393,76</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-67,96; 474,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 206,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 368,82</t>
+          <t>-55,95; 341,17</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 234,5</t>
+          <t>-100,0; 105,91</t>
         </is>
       </c>
     </row>
